--- a/source-data/Enerium_Рецепты.xlsx
+++ b/source-data/Enerium_Рецепты.xlsx
@@ -191,7 +191,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">387a0225ac4ac2ac — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
+          <t xml:space="preserve">13da343c6e69b2a3 — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Первую пробу держали на плитах и каркасах, лицо брали со слепка, жар — из сопла. Энериум держит память, пока Эхо её наполняет. Эхо босса встаёт в Эхо за предмет и 1 душу: сила и бой — как у крафтового босса своего цикла.</t>
+          <t xml:space="preserve">Первую пробу держали на плитах и каркасах, лицо брали со слепка, жар — из сопла. Энериум держит память, пока Эхо её наполняет. Эхо босса встаёт в Эхо за предмет и 1 душу боссом, как босс руины своего цикла (ADR-0039).</t>
         </is>
       </c>
       <c r="L6">
@@ -736,7 +736,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Слепок Элайзиса — город, который обнимает лес, как Подземный лес обнимает свой выводок. Три манка и рог: Мать стаи приходит на голос своих. Эхо босса встаёт в Эхо за предмет и 1 душу: сила и бой — как у крафтового босса своего цикла.</t>
+          <t xml:space="preserve">Слепок Элайзиса — город, который обнимает лес, как Подземный лес обнимает свой выводок. Три манка и рог: Мать стаи приходит на голос своих. Эхо босса встаёт в Эхо за предмет и 1 душу боссом, как босс руины своего цикла (ADR-0039).</t>
         </is>
       </c>
       <c r="L8">
@@ -811,7 +811,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Слепок держит одно лицо — ловчий приходит тенью себя. Многоликий отдаёт ему все лица недели; вторые часы строителей напоминают, кого он кормил, лук и паёк — чем. Пробуждённый босс встаёт в Эхо за предмет и 1 душу: сила — как у крафтового босса на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Слепок держит одно лицо — ловчий приходит тенью себя. Многоликий отдаёт ему все лица недели; вторые часы строителей напоминают, кого он кормил, лук и паёк — чем. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L11">
@@ -946,7 +946,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Рычаг заводит машину на один ход, и она снова встаёт у стены. Многоликий будит её целиком: второе кайло спящих, масло, которым будят уснувшие механизмы, и зубы её же бура. Пробуждённый босс встаёт в Эхо за предмет и 1 душу: сила — как у крафтового босса на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Рычаг заводит машину на один ход, и она снова встаёт у стены. Многоликий будит её целиком: второе кайло спящих, масло, которым будят уснувшие механизмы, и зубы её же бура. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L14">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Парус помнит одну ладью. Многоликий отдаёт ярлу все лица недели — среди них его гребцы; вёсла и семена кромки возвращают ему тот день целиком. Пробуждённый босс встаёт в Эхо за предмет и 1 душу: сила — как у крафтового босса на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Парус помнит одну ладью. Многоликий отдаёт ярлу все лица недели — среди них его гребцы; вёсла и семена кромки возвращают ему тот день целиком. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L17">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вместо лица у Смотрителя — янтарная линза, в груди — первая шестерня. Линзы засыпанной башни, узел и рунные цилиндры его стеллажей. Эхо босса встаёт в Эхо за предмет и 1 душу: сила и бой — как у крафтового босса своего цикла.</t>
+          <t xml:space="preserve">Вместо лица у Смотрителя — янтарная линза, в груди — первая шестерня. Линзы засыпанной башни, узел и рунные цилиндры его стеллажей. Эхо босса встаёт в Эхо за предмет и 1 душу боссом, как босс руины своего цикла (ADR-0039).</t>
         </is>
       </c>
       <c r="L80">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Искусственный Стоун-Хейм — набросок настоящего. Глава наброска откликается на слепок той горы, которую повторяет, на корону на цепи и на болванки без спора. Эхо босса встаёт в Эхо за предмет и 1 душу: сила и бой — как у крафтового босса своего цикла.</t>
+          <t xml:space="preserve">Искусственный Стоун-Хейм — набросок настоящего. Глава наброска откликается на слепок той горы, которую повторяет, на корону на цепи и на болванки без спора. Эхо босса встаёт в Эхо за предмет и 1 душу боссом, как босс руины своего цикла (ADR-0039).</t>
         </is>
       </c>
       <c r="L82">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Переплёт держит одну страницу — книжница помнит одну строку. Многоликий отдаёт ей все лица недели, второй обрывок свитка, карты и звёздные таблицы возвращают страницы. Пробуждённый босс встаёт в Эхо за предмет и 1 душу: сила — как у крафтового босса на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Переплёт держит одну страницу — книжница помнит одну строку. Многоликий отдаёт ей все лица недели, второй обрывок свитка, карты и звёздные таблицы возвращают страницы. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L85">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Гудок помнит одну смену. Многоликий отдаёт бригадиру все лица недели — среди них его смена; лампы и сухари возвращают ему тот день. Пробуждённый босс встаёт в Эхо за предмет и 1 душу: сила — как у крафтового босса на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Гудок помнит одну смену. Многоликий отдаёт бригадиру все лица недели — среди них его смена; лампы и сухари возвращают ему тот день. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L88">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кладка зовёт матку на один день. Многоликий отдаёт ей все лица недели — тех, кто резал письмо; хитин и паутина хранилища. Пробуждённый босс встаёт в Эхо за предмет и 1 душу: сила — как у крафтового босса на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Кладка зовёт матку на один день. Многоликий отдаёт ей все лица недели — тех, кто резал письмо; хитин и паутина хранилища. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L91">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Рычаг заводит привод на один выстрел. Многоликий отдаёт ему все лица недели, заклёпки эстакад и заряженный Рубидиум — весь город, который он стережёт. Пробуждённый босс встаёт в Эхо за предмет и 1 душу: сила — как у крафтового босса на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Рычаг заводит привод на один выстрел. Многоликий отдаёт ему все лица недели, заклёпки эстакад и заряженный Рубидиум — весь город, который он стережёт. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L94">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="H171" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">У Кузнеца за спиной стойка с недокованным оружием, он меняет его в бою. Второй клинок, горновой жар и искры горна — его работа, заказ, что не забрали, — чья-то чужая. Эхо босса встаёт в Эхо за предмет и 1 душу: сила и бой — как у крафтового босса своего цикла.</t>
+          <t xml:space="preserve">У Кузнеца за спиной стойка с недокованным оружием, он меняет его в бою. Второй клинок, горновой жар и искры горна — его работа, заказ, что не забрали, — чья-то чужая. Эхо босса встаёт в Эхо за предмет и 1 душу боссом, как босс руины своего цикла (ADR-0039).</t>
         </is>
       </c>
       <c r="L171">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="H173" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Арена, где бой не кончался, — отражение Арены Сеймура. Воплощение выходит на вызов под знаменем сезона, когда рядом стоит город, который каждый сезон пытается его убить. Эхо босса встаёт в Эхо за предмет и 1 душу: сила и бой — как у крафтового босса своего цикла.</t>
+          <t xml:space="preserve">Арена, где бой не кончался, — отражение Арены Сеймура. Воплощение выходит на вызов под знаменем сезона, когда рядом стоит город, который каждый сезон пытается его убить. Эхо босса встаёт в Эхо за предмет и 1 душу боссом, как босс руины своего цикла (ADR-0039).</t>
         </is>
       </c>
       <c r="L173">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="H176" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Упряжь зовёт зверя, но всадника он не помнит. Многоликий отдаёт ему все лица недели — среди них и всадник; второй наконечник, древний клинок и копыто в подкове. Пробуждённый босс встаёт в Эхо за предмет и 1 душу: сила — как у крафтового босса на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Упряжь зовёт зверя, но всадника он не помнит. Многоликий отдаёт ему все лица недели — среди них и всадник; второй наконечник, древний клинок и копыто в подкове. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L176">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="H179" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Урна зовёт пламя, но оно не помнит, кого стережёт. Многоликий отдаёт ему все лица недели; камень с зарубками и погребальный плащ — всех, кто лёг рядом. Пробуждённый босс встаёт в Эхо за предмет и 1 душу: сила — как у крафтового босса на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Урна зовёт пламя, но оно не помнит, кого стережёт. Многоликий отдаёт ему все лица недели; камень с зарубками и погребальный плащ — всех, кто лёг рядом. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L179">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="H182" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Частокол зовёт таран на один удар. Многоликий отдаёт ему все лица недели — и тех, кто его раскачивал; петли ворот и метательные камни — всю осаду. Пробуждённый босс встаёт в Эхо за предмет и 1 душу: сила — как у крафтового босса на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Частокол зовёт таран на один удар. Многоликий отдаёт ему все лица недели — и тех, кто его раскачивал; петли ворот и метательные камни — всю осаду. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L182">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="H185" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Наковальня зовёт кузнеца на один удар. Многоликий отдаёт ему все лица недели — тех, для кого он ковал; клеймо мастера и пепел горы, когда она дышала. Пробуждённый босс встаёт в Эхо за предмет и 1 душу: сила — как у крафтового босса на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Наковальня зовёт кузнеца на один удар. Многоликий отдаёт ему все лица недели — тех, для кого он ковал; клеймо мастера и пепел горы, когда она дышала. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L185">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="H188" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вызов зовёт учителя на один бой. Многоликий отдаёт ему все лица недели — среди них его ученики; сколы именных камней и заряженный Нитриум разгорают всё, что в нём было. Пробуждённый босс встаёт в Эхо за предмет и 1 душу: сила — как у крафтового босса на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Вызов зовёт учителя на один бой. Многоликий отдаёт ему все лица недели — среди них его ученики; сколы именных камней и заряженный Нитриум разгорают всё, что в нём было. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L188">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="H260" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Залы у водопадов — отражение города, где вершат приговор. Помост на шлюзовых замках, чешуя тёмной воды — и колокол, который звонит перед исполнением. Эхо босса встаёт в Эхо за предмет и 1 душу: сила и бой — как у крафтового босса своего цикла.</t>
+          <t xml:space="preserve">Залы у водопадов — отражение города, где вершат приговор. Помост на шлюзовых замках, чешуя тёмной воды — и колокол, который звонит перед исполнением. Эхо босса встаёт в Эхо за предмет и 1 душу боссом, как босс руины своего цикла (ADR-0039).</t>
         </is>
       </c>
       <c r="L260">
@@ -12241,7 +12241,7 @@
       </c>
       <c r="H262" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Город суда — набросок Лайтен-Гарда. Судья с весами выходит, когда рядом слепок города, где приговор признают везде, и весы, где равным судят равное. Эхо босса встаёт в Эхо за предмет и 1 душу: сила и бой — как у крафтового босса своего цикла.</t>
+          <t xml:space="preserve">Город суда — набросок Лайтен-Гарда. Судья с весами выходит, когда рядом слепок города, где приговор признают везде, и весы, где равным судят равное. Эхо босса встаёт в Эхо за предмет и 1 душу боссом, как босс руины своего цикла (ADR-0039).</t>
         </is>
       </c>
       <c r="L262">
@@ -12316,7 +12316,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="H265" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Колокол звонит один раз — хранительница помнит один день. Многоликий отдаёт ей все лица недели; вторая чаша, обет у воды и заповедь на камне возвращают ей святилище целиком. Пробуждённый босс встаёт в Эхо за предмет и 1 душу: сила — как у крафтового босса на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Колокол звонит один раз — хранительница помнит один день. Многоликий отдаёт ей все лица недели; вторая чаша, обет у воды и заповедь на камне возвращают ей святилище целиком. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L265">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -12511,7 +12511,7 @@
       </c>
       <c r="H268" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Маяк зажигает свет на одну ночь. Многоликий отдаёт спящему все лица недели — корабли, что ходили мимо; чешуя и ребро его рода. Пробуждённый босс встаёт в Эхо за предмет и 1 душу: сила — как у крафтового босса на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Маяк зажигает свет на одну ночь. Многоликий отдаёт спящему все лица недели — корабли, что ходили мимо; чешуя и ребро его рода. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L268">
@@ -12586,7 +12586,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -12646,7 +12646,7 @@
       </c>
       <c r="H271" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Стакан заводит машину на один бросок. Многоликий отдаёт ей все лица недели — всех, за кого она бросала; плиты с исходами и мел черты. Пробуждённый босс встаёт в Эхо за предмет и 1 душу: сила — как у крафтового босса на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Стакан заводит машину на один бросок. Многоликий отдаёт ей все лица недели — всех, за кого она бросала; плиты с исходами и мел черты. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L271">
@@ -12721,7 +12721,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -12781,7 +12781,7 @@
       </c>
       <c r="H274" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Затвор поднимает одну воду. Многоликий отдаёт смотрителю все лица недели — корабли, что проходили; отметки уровня и угорь, переживший реку. Пробуждённый босс встаёт в Эхо за предмет и 1 душу: сила — как у крафтового босса на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Затвор поднимает одну воду. Многоликий отдаёт смотрителю все лица недели — корабли, что проходили; отметки уровня и угорь, переживший реку. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L274">
@@ -12856,7 +12856,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="H277" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мутная вода зовёт стража одной арки. Многоликий отдаёт ему все лица недели — всех, кто проходил под ней; канаты гавани и Паладиум — все арки города. Пробуждённый босс встаёт в Эхо за предмет и 1 душу: сила — как у крафтового босса на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Мутная вода зовёт стража одной арки. Многоликий отдаёт ему все лица недели — всех, кто проходил под ней; канаты гавани и Паладиум — все арки города. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L277">
@@ -15551,7 +15551,7 @@
       </c>
       <c r="H335" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Поздний источник снаряжения — дорогие рецепты из трофеев крафтовых боссов (§12.3, §21.3). Закалённый брусок — основа под предмет, клеймо — его имя, звенья — оковка.</t>
+          <t xml:space="preserve">Поздний источник снаряжения — дорогие рецепты из трофеев призванных врагов (§12.3, §21.3). Закалённый брусок — основа под предмет, клеймо — его имя, звенья — оковка.</t>
         </is>
       </c>
       <c r="L335">
@@ -16411,7 +16411,7 @@
       </c>
       <c r="H354" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зал часов полон застрявших искателей; искать учат в Эндалоре. Тот, кто не дошёл, делает свой шаг, когда рядом город школы Времени и часы, в которых песок пошёл. Эхо босса встаёт в Эхо за предмет и 1 душу: сила и бой — как у крафтового босса своего цикла.</t>
+          <t xml:space="preserve">Зал часов полон застрявших искателей; искать учат в Эндалоре. Тот, кто не дошёл, делает свой шаг, когда рядом город школы Времени и часы, в которых песок пошёл. Эхо босса встаёт в Эхо за предмет и 1 душу боссом, как босс руины своего цикла (ADR-0039).</t>
         </is>
       </c>
       <c r="L354">
@@ -16501,7 +16501,7 @@
       </c>
       <c r="H356" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лабиринт у воронки — время, которое уходит: стены встают иначе каждый день. Архитектор приходит на свой отвес и на стену, которую надо переставить. Эхо босса встаёт в Эхо за предмет и 1 душу: сила и бой — как у крафтового босса своего цикла.</t>
+          <t xml:space="preserve">Лабиринт у воронки — время, которое уходит: стены встают иначе каждый день. Архитектор приходит на свой отвес и на стену, которую надо переставить. Эхо босса встаёт в Эхо за предмет и 1 душу боссом, как босс руины своего цикла (ADR-0039).</t>
         </is>
       </c>
       <c r="L356">
@@ -16576,7 +16576,7 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
@@ -16636,7 +16636,7 @@
       </c>
       <c r="H359" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Узел помнит одну глубину, и ту чужую. Многоликий отдаёт ей все лица недели, и счёт возвращается весь: второй свисток, кости чужого хода и метки тех, кто спускался. Пробуждённый босс встаёт в Эхо за предмет и 1 душу: сила — как у крафтового босса на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Узел помнит одну глубину, и ту чужую. Многоликий отдаёт ей все лица недели, и счёт возвращается весь: второй свисток, кости чужого хода и метки тех, кто спускался. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L359">
@@ -16711,7 +16711,7 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
@@ -16771,7 +16771,7 @@
       </c>
       <c r="H362" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Полдень сдвигает тень на один час. Многоликий отдаёт ей все лица недели; плиты циферблата и перья жаворонков — все часы от рассвета. Пробуждённый босс встаёт в Эхо за предмет и 1 душу: сила — как у крафтового босса на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Полдень сдвигает тень на один час. Многоликий отдаёт ей все лица недели; плиты циферблата и перья жаворонков — все часы от рассвета. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L362">
@@ -16846,7 +16846,7 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
@@ -16906,7 +16906,7 @@
       </c>
       <c r="H365" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Подорожная ведёт погонщика на один день. Многоликий отдаёт ему все лица недели — тех, кто его ждал; мулы и треснувшие ящики — весь караван. Пробуждённый босс встаёт в Эхо за предмет и 1 душу: сила — как у крафтового босса на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Подорожная ведёт погонщика на один день. Многоликий отдаёт ему все лица недели — тех, кто его ждал; мулы и треснувшие ящики — весь караван. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L365">
@@ -16981,7 +16981,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
@@ -17041,7 +17041,7 @@
       </c>
       <c r="H368" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Чашки зовут её на один вечер. Многоликий отдаёт ей все лица недели — среди них и то, которого она ждёт; песня у окна и покрывало на кресле возвращают дом целиком. Пробуждённый босс встаёт в Эхо за предмет и 1 душу: сила — как у крафтового босса на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Чашки зовут её на один вечер. Многоликий отдаёт ей все лица недели — среди них и то, которого она ждёт; песня у окна и покрывало на кресле возвращают дом целиком. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L368">
@@ -17116,7 +17116,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
@@ -17176,7 +17176,7 @@
       </c>
       <c r="H371" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тетива доводит прыжок до конца один раз. Многоликий отдаёт зверю все лица недели — охотников; шерсть, что оторвала стрела, и поводок гончей, что за ним гналась. Пробуждённый босс встаёт в Эхо за предмет и 1 душу: сила — как у крафтового босса на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Тетива доводит прыжок до конца один раз. Многоликий отдаёт зверю все лица недели — охотников; шерсть, что оторвала стрела, и поводок гончей, что за ним гналась. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L371">
@@ -17251,7 +17251,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
@@ -17311,7 +17311,7 @@
       </c>
       <c r="H374" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вызов зовёт её на один Довод. Многоликий отдаёт ей все лица недели — всех, кто признавал вслух; синие накопители и гостевые печати держат её в городе, друза Энериума — время, которого в Доводе всегда не хватает. Пробуждённый босс встаёт в Эхо за предмет и 1 душу: сила — как у крафтового босса на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Вызов зовёт её на один Довод. Многоликий отдаёт ей все лица недели — всех, кто признавал вслух; синие накопители и гостевые печати держат её в городе, друза Энериума — время, которого в Доводе всегда не хватает. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L374">
@@ -20881,7 +20881,7 @@
       </c>
       <c r="H452" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Правая рука стоит у пустых изложниц. Свечи Прозревших и цвет, поднявший мёртвых, — её свита; друза Энериума держит память о том, чего не должно было случиться. Эхо босса встаёт в Эхо за предмет и 1 душу: сила и бой — как у крафтового босса своего цикла.</t>
+          <t xml:space="preserve">Правая рука стоит у пустых изложниц. Свечи Прозревших и цвет, поднявший мёртвых, — её свита; друза Энериума держит память о том, чего не должно было случиться. Эхо босса встаёт в Эхо за предмет и 1 душу боссом, как босс руины своего цикла (ADR-0039).</t>
         </is>
       </c>
       <c r="L452">
@@ -20981,7 +20981,7 @@
       </c>
       <c r="H454" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Хранитель помнит мир, когда город стоял на земле. Слепок того города, Некрониум, который плавит Энериум, и друза — чтобы хватило времени. Эхо босса встаёт в Эхо за предмет и 1 душу: сила и бой — как у крафтового босса своего цикла.</t>
+          <t xml:space="preserve">Хранитель помнит мир, когда город стоял на земле. Слепок того города, Некрониум, который плавит Энериум, и друза — чтобы хватило времени. Эхо босса встаёт в Эхо за предмет и 1 душу боссом, как босс руины своего цикла (ADR-0039).</t>
         </is>
       </c>
       <c r="L454">
@@ -21066,7 +21066,7 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
@@ -21131,7 +21131,7 @@
       </c>
       <c r="H457" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отливке нужно лицо — слепок даёт одно, Многоликий отдаёт все лица недели. Второй дикий карст, пустая изложница и пепел застывшего лагеря. Пробуждённый босс встаёт в Эхо за предмет и 1 душу: сила — как у крафтового босса на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Отливке нужно лицо — слепок даёт одно, Многоликий отдаёт все лица недели. Второй дикий карст, пустая изложница и пепел застывшего лагеря. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L457">
@@ -21216,7 +21216,7 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
@@ -21281,7 +21281,7 @@
       </c>
       <c r="H460" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Смена зовёт одного мастера. Многоликий отдаёт ему все лица недели — всю смену; верстаки и лампы мёртвой смены. Пробуждённый босс встаёт в Эхо за предмет и 1 душу: сила — как у крафтового босса на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Смена зовёт одного мастера. Многоликий отдаёт ему все лица недели — всю смену; верстаки и лампы мёртвой смены. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L460">
@@ -21366,7 +21366,7 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
@@ -21431,7 +21431,7 @@
       </c>
       <c r="H463" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Урок зовёт учителя на один час. Многоликий отдаёт ему все лица недели — его учеников; сколы Оболочки и разбитые часы — то, что его изменило. Пробуждённый босс встаёт в Эхо за предмет и 1 душу: сила — как у крафтового босса на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Урок зовёт учителя на один час. Многоликий отдаёт ему все лица недели — его учеников; сколы Оболочки и разбитые часы — то, что его изменило. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L463">
@@ -21516,7 +21516,7 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
@@ -21581,7 +21581,7 @@
       </c>
       <c r="H466" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Глина зовёт первого на один день. Многоликий отдаёт ему все лица недели — выбрать своё; первые сколы и Некрониум — откуда он пришёл. Пробуждённый босс встаёт в Эхо за предмет и 1 душу: сила — как у крафтового босса на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Глина зовёт первого на один день. Многоликий отдаёт ему все лица недели — выбрать своё; первые сколы и Некрониум — откуда он пришёл. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L466">
@@ -23701,7 +23701,7 @@
       </c>
       <c r="H508" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Самый дорогой рецепт талисманов: трофеи двух последних крафтовых боссов, Некрониум, пустая форма и обеты, данные у воды.</t>
+          <t xml:space="preserve">Самый дорогой рецепт талисманов: трофеи двух последних призванных врагов, Некрониум, пустая форма и обеты, данные у воды.</t>
         </is>
       </c>
       <c r="L508">
@@ -24805,7 +24805,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крафтовый босс</t>
+          <t xml:space="preserve">Призванный враг</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">

--- a/source-data/Enerium_Рецепты.xlsx
+++ b/source-data/Enerium_Рецепты.xlsx
@@ -179,7 +179,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-01 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
+          <t xml:space="preserve">2026-10-07 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
         </is>
       </c>
     </row>
@@ -191,7 +191,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">13da343c6e69b2a3 — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
+          <t xml:space="preserve">2f76202093f27535 — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
         </is>
       </c>
     </row>
@@ -319,8 +319,8 @@
 III — слабые, почти незаметные намёки — слово-отзвук без имени тайны (ADR-0022: намёки на Странника — с цикла III)
 IV — заметнее, но всё ещё намёки: иносказание, без прямых имён и формулировок тайны
 V — намёки очевиднее («начиная с 5 будут намёки»); прямого раскрытия §38 нет
-VI — только для команды: здесь тайны названы прямо
-Ступени слов: D — прямое раскрытие — только цикл VI, для команды; H3 — явный намёк — с цикла V; H2 — заметный намёк — с цикла IV; H1 — слабый намёк, слово-отзвук — с цикла III.
+VI — раскрытие: в текстах игрока цикла VI тайны могут быть названы прямо (ADR-0054); в текстах циклов I–V — нет
+Ступени слов: D — прямое раскрытие — только с цикла VI: игрок получает его в игре, раньше — нет; H3 — явный намёк — с цикла V; H2 — заметный намёк — с цикла IV; H1 — слабый намёк, слово-отзвук — с цикла III.
 Проверка — node tools/content-gen/tables/check_spoilers.js; все совпадения по циклам — «Реестр имён», лист «Намёки по циклам».</t>
         </is>
       </c>
@@ -871,7 +871,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Слепок держит одно лицо — ловчий приходит тенью себя. Многоликий отдаёт ему все лица недели; вторые часы строителей напоминают, кого он кормил, лук и паёк — чем. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Слепок держит одно лицо — ловчий приходит тенью себя. Многоликий отдаёт ему все лица недели; вторые часы строителей напоминают, кого он кормил, лук и паёк — чем. Пробуждённый босс встаёт в Эхо за предмет и 1 душу врагом типа «Пробуждённый» — шестой ступени (ADR-0039, ADR-0054): раунды и иммунитет — его типа, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L11">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Рычаг заводит машину на один ход, и она снова встаёт у стены. Многоликий будит её целиком: второе кайло спящих, масло, которым будят уснувшие механизмы, и зубы её же бура. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Рычаг заводит машину на один ход, и она снова встаёт у стены. Многоликий будит её целиком: второе кайло спящих, масло, которым будят уснувшие механизмы, и зубы её же бура. Пробуждённый босс встаёт в Эхо за предмет и 1 душу врагом типа «Пробуждённый» — шестой ступени (ADR-0039, ADR-0054): раунды и иммунитет — его типа, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L14">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Парус помнит одну ладью. Многоликий отдаёт ярлу все лица недели — среди них его гребцы; вёсла и семена кромки возвращают ему тот день целиком. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Парус помнит одну ладью. Многоликий отдаёт ярлу все лица недели — среди них его гребцы; вёсла и семена кромки возвращают ему тот день целиком. Пробуждённый босс встаёт в Эхо за предмет и 1 душу врагом типа «Пробуждённый» — шестой ступени (ADR-0039, ADR-0054): раунды и иммунитет — его типа, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L17">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Переплёт держит одну страницу — книжница помнит одну строку. Многоликий отдаёт ей все лица недели, второй обрывок свитка, карты и звёздные таблицы возвращают страницы. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Переплёт держит одну страницу — книжница помнит одну строку. Многоликий отдаёт ей все лица недели, второй обрывок свитка, карты и звёздные таблицы возвращают страницы. Пробуждённый босс встаёт в Эхо за предмет и 1 душу врагом типа «Пробуждённый» — шестой ступени (ADR-0039, ADR-0054): раунды и иммунитет — его типа, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L85">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Гудок помнит одну смену. Многоликий отдаёт бригадиру все лица недели — среди них его смена; лампы и сухари возвращают ему тот день. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Гудок помнит одну смену. Многоликий отдаёт бригадиру все лица недели — среди них его смена; лампы и сухари возвращают ему тот день. Пробуждённый босс встаёт в Эхо за предмет и 1 душу врагом типа «Пробуждённый» — шестой ступени (ADR-0039, ADR-0054): раунды и иммунитет — его типа, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L88">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кладка зовёт матку на один день. Многоликий отдаёт ей все лица недели — тех, кто резал письмо; хитин и паутина хранилища. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Кладка зовёт матку на один день. Многоликий отдаёт ей все лица недели — тех, кто резал письмо; хитин и паутина хранилища. Пробуждённый босс встаёт в Эхо за предмет и 1 душу врагом типа «Пробуждённый» — шестой ступени (ADR-0039, ADR-0054): раунды и иммунитет — его типа, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L91">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Рычаг заводит привод на один выстрел. Многоликий отдаёт ему все лица недели, заклёпки эстакад и заряженный Рубидиум — весь город, который он стережёт. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Рычаг заводит привод на один выстрел. Многоликий отдаёт ему все лица недели, заклёпки эстакад и заряженный Рубидиум — весь город, который он стережёт. Пробуждённый босс встаёт в Эхо за предмет и 1 душу врагом типа «Пробуждённый» — шестой ступени (ADR-0039, ADR-0054): раунды и иммунитет — его типа, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L94">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="H176" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Упряжь зовёт зверя, но всадника он не помнит. Многоликий отдаёт ему все лица недели — среди них и всадник; второй наконечник, древний клинок и копыто в подкове. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Упряжь зовёт зверя, но всадника он не помнит. Многоликий отдаёт ему все лица недели — среди них и всадник; второй наконечник, древний клинок и копыто в подкове. Пробуждённый босс встаёт в Эхо за предмет и 1 душу врагом типа «Пробуждённый» — шестой ступени (ADR-0039, ADR-0054): раунды и иммунитет — его типа, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L176">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="H179" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Урна зовёт пламя, но оно не помнит, кого стережёт. Многоликий отдаёт ему все лица недели; камень с зарубками и погребальный плащ — всех, кто лёг рядом. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Урна зовёт пламя, но оно не помнит, кого стережёт. Многоликий отдаёт ему все лица недели; камень с зарубками и погребальный плащ — всех, кто лёг рядом. Пробуждённый босс встаёт в Эхо за предмет и 1 душу врагом типа «Пробуждённый» — шестой ступени (ADR-0039, ADR-0054): раунды и иммунитет — его типа, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L179">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="H182" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Частокол зовёт таран на один удар. Многоликий отдаёт ему все лица недели — и тех, кто его раскачивал; петли ворот и метательные камни — всю осаду. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Частокол зовёт таран на один удар. Многоликий отдаёт ему все лица недели — и тех, кто его раскачивал; петли ворот и метательные камни — всю осаду. Пробуждённый босс встаёт в Эхо за предмет и 1 душу врагом типа «Пробуждённый» — шестой ступени (ADR-0039, ADR-0054): раунды и иммунитет — его типа, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L182">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="H185" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Наковальня зовёт кузнеца на один удар. Многоликий отдаёт ему все лица недели — тех, для кого он ковал; клеймо мастера и пепел горы, когда она дышала. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Наковальня зовёт кузнеца на один удар. Многоликий отдаёт ему все лица недели — тех, для кого он ковал; клеймо мастера и пепел горы, когда она дышала. Пробуждённый босс встаёт в Эхо за предмет и 1 душу врагом типа «Пробуждённый» — шестой ступени (ADR-0039, ADR-0054): раунды и иммунитет — его типа, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L185">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="H188" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вызов зовёт учителя на один бой. Многоликий отдаёт ему все лица недели — среди них его ученики; сколы именных камней и заряженный Нитриум разгорают всё, что в нём было. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Вызов зовёт учителя на один бой. Многоликий отдаёт ему все лица недели — среди них его ученики; сколы именных камней и заряженный Нитриум разгорают всё, что в нём было. Пробуждённый босс встаёт в Эхо за предмет и 1 душу врагом типа «Пробуждённый» — шестой ступени (ADR-0039, ADR-0054): раунды и иммунитет — его типа, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L188">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="H265" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Колокол звонит один раз — хранительница помнит один день. Многоликий отдаёт ей все лица недели; вторая чаша, обет у воды и заповедь на камне возвращают ей святилище целиком. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Колокол звонит один раз — хранительница помнит один день. Многоликий отдаёт ей все лица недели; вторая чаша, обет у воды и заповедь на камне возвращают ей святилище целиком. Пробуждённый босс встаёт в Эхо за предмет и 1 душу врагом типа «Пробуждённый» — шестой ступени (ADR-0039, ADR-0054): раунды и иммунитет — его типа, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L265">
@@ -12511,7 +12511,7 @@
       </c>
       <c r="H268" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Маяк зажигает свет на одну ночь. Многоликий отдаёт спящему все лица недели — корабли, что ходили мимо; чешуя и ребро его рода. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Маяк зажигает свет на одну ночь. Многоликий отдаёт спящему все лица недели — корабли, что ходили мимо; чешуя и ребро его рода. Пробуждённый босс встаёт в Эхо за предмет и 1 душу врагом типа «Пробуждённый» — шестой ступени (ADR-0039, ADR-0054): раунды и иммунитет — его типа, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L268">
@@ -12646,7 +12646,7 @@
       </c>
       <c r="H271" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Стакан заводит машину на один бросок. Многоликий отдаёт ей все лица недели — всех, за кого она бросала; плиты с исходами и мел черты. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Стакан заводит машину на один бросок. Многоликий отдаёт ей все лица недели — всех, за кого она бросала; плиты с исходами и мел черты. Пробуждённый босс встаёт в Эхо за предмет и 1 душу врагом типа «Пробуждённый» — шестой ступени (ADR-0039, ADR-0054): раунды и иммунитет — его типа, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L271">
@@ -12781,7 +12781,7 @@
       </c>
       <c r="H274" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Затвор поднимает одну воду. Многоликий отдаёт смотрителю все лица недели — корабли, что проходили; отметки уровня и угорь, переживший реку. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Затвор поднимает одну воду. Многоликий отдаёт смотрителю все лица недели — корабли, что проходили; отметки уровня и угорь, переживший реку. Пробуждённый босс встаёт в Эхо за предмет и 1 душу врагом типа «Пробуждённый» — шестой ступени (ADR-0039, ADR-0054): раунды и иммунитет — его типа, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L274">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="H277" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мутная вода зовёт стража одной арки. Многоликий отдаёт ему все лица недели — всех, кто проходил под ней; канаты гавани и Паладиум — все арки города. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Мутная вода зовёт стража одной арки. Многоликий отдаёт ему все лица недели — всех, кто проходил под ней; канаты гавани и Паладиум — все арки города. Пробуждённый босс встаёт в Эхо за предмет и 1 душу врагом типа «Пробуждённый» — шестой ступени (ADR-0039, ADR-0054): раунды и иммунитет — его типа, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L277">
@@ -16636,7 +16636,7 @@
       </c>
       <c r="H359" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Узел помнит одну глубину, и ту чужую. Многоликий отдаёт ей все лица недели, и счёт возвращается весь: второй свисток, кости чужого хода и метки тех, кто спускался. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Узел помнит одну глубину, и ту чужую. Многоликий отдаёт ей все лица недели, и счёт возвращается весь: второй свисток, кости чужого хода и метки тех, кто спускался. Пробуждённый босс встаёт в Эхо за предмет и 1 душу врагом типа «Пробуждённый» — шестой ступени (ADR-0039, ADR-0054): раунды и иммунитет — его типа, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L359">
@@ -16771,7 +16771,7 @@
       </c>
       <c r="H362" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Полдень сдвигает тень на один час. Многоликий отдаёт ей все лица недели; плиты циферблата и перья жаворонков — все часы от рассвета. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Полдень сдвигает тень на один час. Многоликий отдаёт ей все лица недели; плиты циферблата и перья жаворонков — все часы от рассвета. Пробуждённый босс встаёт в Эхо за предмет и 1 душу врагом типа «Пробуждённый» — шестой ступени (ADR-0039, ADR-0054): раунды и иммунитет — его типа, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L362">
@@ -16906,7 +16906,7 @@
       </c>
       <c r="H365" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Подорожная ведёт погонщика на один день. Многоликий отдаёт ему все лица недели — тех, кто его ждал; мулы и треснувшие ящики — весь караван. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Подорожная ведёт погонщика на один день. Многоликий отдаёт ему все лица недели — тех, кто его ждал; мулы и треснувшие ящики — весь караван. Пробуждённый босс встаёт в Эхо за предмет и 1 душу врагом типа «Пробуждённый» — шестой ступени (ADR-0039, ADR-0054): раунды и иммунитет — его типа, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L365">
@@ -17041,7 +17041,7 @@
       </c>
       <c r="H368" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Чашки зовут её на один вечер. Многоликий отдаёт ей все лица недели — среди них и то, которого она ждёт; песня у окна и покрывало на кресле возвращают дом целиком. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Чашки зовут её на один вечер. Многоликий отдаёт ей все лица недели — среди них и то, которого она ждёт; песня у окна и покрывало на кресле возвращают дом целиком. Пробуждённый босс встаёт в Эхо за предмет и 1 душу врагом типа «Пробуждённый» — шестой ступени (ADR-0039, ADR-0054): раунды и иммунитет — его типа, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L368">
@@ -17176,7 +17176,7 @@
       </c>
       <c r="H371" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тетива доводит прыжок до конца один раз. Многоликий отдаёт зверю все лица недели — охотников; шерсть, что оторвала стрела, и поводок гончей, что за ним гналась. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Тетива доводит прыжок до конца один раз. Многоликий отдаёт зверю все лица недели — охотников; шерсть, что оторвала стрела, и поводок гончей, что за ним гналась. Пробуждённый босс встаёт в Эхо за предмет и 1 душу врагом типа «Пробуждённый» — шестой ступени (ADR-0039, ADR-0054): раунды и иммунитет — его типа, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L371">
@@ -17311,7 +17311,7 @@
       </c>
       <c r="H374" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вызов зовёт её на один Довод. Многоликий отдаёт ей все лица недели — всех, кто признавал вслух; синие накопители и гостевые печати держат её в городе, друза Энериума — время, которого в Доводе всегда не хватает. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Вызов зовёт её на один Довод. Многоликий отдаёт ей все лица недели — всех, кто признавал вслух; синие накопители и гостевые печати держат её в городе, друза Энериума — время, которого в Доводе всегда не хватает. Пробуждённый босс встаёт в Эхо за предмет и 1 душу врагом типа «Пробуждённый» — шестой ступени (ADR-0039, ADR-0054): раунды и иммунитет — его типа, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L374">
@@ -21131,7 +21131,7 @@
       </c>
       <c r="H457" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отливке нужно лицо — слепок даёт одно, Многоликий отдаёт все лица недели. Второй дикий карст, пустая изложница и пепел застывшего лагеря. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Отливке нужно лицо — слепок даёт одно, Многоликий отдаёт все лица недели. Второй дикий карст, пустая изложница и пепел застывшего лагеря. Пробуждённый босс встаёт в Эхо за предмет и 1 душу врагом типа «Пробуждённый» — шестой ступени (ADR-0039, ADR-0054): раунды и иммунитет — его типа, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L457">
@@ -21281,7 +21281,7 @@
       </c>
       <c r="H460" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Смена зовёт одного мастера. Многоликий отдаёт ему все лица недели — всю смену; верстаки и лампы мёртвой смены. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Смена зовёт одного мастера. Многоликий отдаёт ему все лица недели — всю смену; верстаки и лампы мёртвой смены. Пробуждённый босс встаёт в Эхо за предмет и 1 душу врагом типа «Пробуждённый» — шестой ступени (ADR-0039, ADR-0054): раунды и иммунитет — его типа, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L460">
@@ -21431,7 +21431,7 @@
       </c>
       <c r="H463" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Урок зовёт учителя на один час. Многоликий отдаёт ему все лица недели — его учеников; сколы Оболочки и разбитые часы — то, что его изменило. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Урок зовёт учителя на один час. Многоликий отдаёт ему все лица недели — его учеников; сколы Оболочки и разбитые часы — то, что его изменило. Пробуждённый босс встаёт в Эхо за предмет и 1 душу врагом типа «Пробуждённый» — шестой ступени (ADR-0039, ADR-0054): раунды и иммунитет — его типа, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L463">
@@ -21581,7 +21581,7 @@
       </c>
       <c r="H466" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Глина зовёт первого на один день. Многоликий отдаёт ему все лица недели — выбрать своё; первые сколы и Некрониум — откуда он пришёл. Пробуждённый встаёт в Эхо за предмет и 1 душу Забытым — высшей ступенью врага (ADR-0039): 50 раундов, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
+          <t xml:space="preserve">Глина зовёт первого на один день. Многоликий отдаёт ему все лица недели — выбрать своё; первые сколы и Некрониум — откуда он пришёл. Пробуждённый босс встаёт в Эхо за предмет и 1 душу врагом типа «Пробуждённый» — шестой ступени (ADR-0039, ADR-0054): раунды и иммунитет — его типа, сила своего типа на 1 цикл выше, трофей — свой, сундук — на 1 ступень выше.</t>
         </is>
       </c>
       <c r="L466">
